--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127048898</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127048897</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127048898</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127048897</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127048898</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127048974</v>
       </c>
       <c r="B4" t="n">
-        <v>109283</v>
+        <v>109260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127048966</v>
       </c>
       <c r="B5" t="n">
-        <v>98434</v>
+        <v>98414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127048897</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118273324</v>
+        <v>127048896</v>
       </c>
       <c r="B2" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lukaremyr (Lukaremyr), Gtl</t>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720364</v>
+        <v>720385</v>
       </c>
       <c r="R2" t="n">
-        <v>6369292</v>
+        <v>6369162</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,30 +761,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tall med födosök av spillkråka.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127048898</v>
+        <v>127048897</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720355</v>
+        <v>720397</v>
       </c>
       <c r="R3" t="n">
-        <v>6369259</v>
+        <v>6369194</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127048974</v>
+        <v>127048898</v>
       </c>
       <c r="B4" t="n">
-        <v>109283</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720365</v>
+        <v>720355</v>
       </c>
       <c r="R4" t="n">
-        <v>6369263</v>
+        <v>6369259</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall med födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,57 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127048966</v>
+        <v>118273324</v>
       </c>
       <c r="B5" t="n">
-        <v>98434</v>
+        <v>43467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Lukaremyr, Lukaremyr, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720405</v>
+        <v>720364</v>
       </c>
       <c r="R5" t="n">
-        <v>6369211</v>
+        <v>6369292</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,48 +1077,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127048897</v>
+        <v>127049136</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>43299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1125,22 +1121,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala, Lauritse 1:38., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720397</v>
+        <v>720280</v>
       </c>
       <c r="R6" t="n">
-        <v>6369194</v>
+        <v>6369279</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,6 +1185,11 @@
           <t>2025-07-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1186,7 +1201,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tall med födosök av spillkråka.</t>
+          <t>Alvar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1201,6 +1216,979 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127048961</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127048966</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720405</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6369211</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127048979</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6369218</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127048957</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720377</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6369160</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127048960</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127048977</v>
+      </c>
+      <c r="B12" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720338</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6369218</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127048980</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720280</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6369279</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127048974</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720365</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6369263</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127048981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720280</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6369279</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,64 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049136</v>
+        <v>134659097</v>
       </c>
       <c r="B6" t="n">
-        <v>43299</v>
+        <v>43472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101260</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720280</v>
+        <v>720397</v>
       </c>
       <c r="R6" t="n">
-        <v>6369279</v>
+        <v>6369231</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1177,17 +1158,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Alvar 100 m x 100 m.</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,78 +1189,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Alvar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127048961</v>
+        <v>134659099</v>
       </c>
       <c r="B7" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720387</v>
+        <v>720431</v>
       </c>
       <c r="R7" t="n">
-        <v>6369164</v>
+        <v>6369229</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1270,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,78 +1296,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127048966</v>
+        <v>134659101</v>
       </c>
       <c r="B8" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720405</v>
+        <v>720424</v>
       </c>
       <c r="R8" t="n">
-        <v>6369211</v>
+        <v>6369221</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,12 +1377,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,69 +1408,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127048979</v>
+        <v>134659102</v>
       </c>
       <c r="B9" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720338</v>
+        <v>720414</v>
       </c>
       <c r="R9" t="n">
-        <v>6369218</v>
+        <v>6369197</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,12 +1489,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 st, förökningsyta</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,78 +1520,64 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127048957</v>
+        <v>134659103</v>
       </c>
       <c r="B10" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720377</v>
+        <v>720383</v>
       </c>
       <c r="R10" t="n">
-        <v>6369160</v>
+        <v>6369171</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1617,12 +1601,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 st förökningsyta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,78 +1632,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127048960</v>
+        <v>134659105</v>
       </c>
       <c r="B11" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720387</v>
+        <v>720368</v>
       </c>
       <c r="R11" t="n">
-        <v>6369164</v>
+        <v>6369154</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,12 +1713,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,31 +1739,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127048977</v>
+        <v>134659107</v>
       </c>
       <c r="B12" t="n">
-        <v>108116</v>
+        <v>43472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,46 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720338</v>
+        <v>720371</v>
       </c>
       <c r="R12" t="n">
-        <v>6369218</v>
+        <v>6369183</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,12 +1820,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,31 +1846,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127048980</v>
+        <v>134659108</v>
       </c>
       <c r="B13" t="n">
-        <v>104640</v>
+        <v>43472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720280</v>
+        <v>720333</v>
       </c>
       <c r="R13" t="n">
-        <v>6369279</v>
+        <v>6369254</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1941,17 +1927,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Alvar 100 m x 100 m.</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,31 +1953,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Alvar.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127048974</v>
+        <v>134659347</v>
       </c>
       <c r="B14" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,37 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720365</v>
+        <v>720354</v>
       </c>
       <c r="R14" t="n">
-        <v>6369263</v>
+        <v>6369272</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,12 +2034,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,31 +2065,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127048981</v>
+        <v>134659349</v>
       </c>
       <c r="B15" t="n">
-        <v>107517</v>
+        <v>43472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,37 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720280</v>
+        <v>720389</v>
       </c>
       <c r="R15" t="n">
-        <v>6369279</v>
+        <v>6369245</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,17 +2146,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Alvar 100 m x 100 m.</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,24 +2177,1790 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Alvar.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134659352</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720393</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6369214</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134659353</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6369202</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134659355</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720389</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6369181</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134659357</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720366</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6369161</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134659362</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720370</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6369166</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134659364</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720360</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6369253</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127049136</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720280</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6369279</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127048961</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127048966</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720405</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6369211</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127048979</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720338</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6369218</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127048957</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720377</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6369160</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127048960</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127048977</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720338</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6369218</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127048980</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720280</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6369279</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127048974</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720365</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6369263</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127048981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720280</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6369279</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Alvar 100 m x 100 m.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -2069,12 +2069,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2293,12 +2293,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,12 +2517,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2629,12 +2629,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2853,12 +2853,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 20833-2024 artfynd.xlsx
+++ b/artfynd/A 20833-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273324</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659101</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659102</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659103</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659105</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659107</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659108</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659347</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659349</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659352</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659353</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2526,6 +2611,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659355</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659357</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659362</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2862,6 +2962,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659364</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2988,6 +3093,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049136</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3099,6 +3209,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048961</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3210,6 +3325,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048966</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3312,6 +3432,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048979</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3423,6 +3548,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048957</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3534,6 +3664,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048960</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3645,6 +3780,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048977</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3752,6 +3892,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048980</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3854,6 +3999,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048974</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3961,8 +4111,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>